--- a/data/LME_002/LME_002.xlsx
+++ b/data/LME_002/LME_002.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,1035 +532,1066 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1950-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>212</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1950-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>170</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>catch_tonnes</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_tonnes</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_over_npp_percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B13" t="n">
-        <v>391288.949</v>
-      </c>
-      <c r="C13" t="n">
-        <v>271993731.416</v>
-      </c>
-      <c r="D13" t="n">
-        <v>123.6374</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B14" t="n">
-        <v>382769.719</v>
-      </c>
-      <c r="C14" t="n">
-        <v>323530143.714</v>
-      </c>
-      <c r="D14" t="n">
-        <v>147.0638</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>catch_tonnes</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_tonnes</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_over_npp_percent</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B15" t="n">
-        <v>277460.614</v>
+        <v>391288.949</v>
       </c>
       <c r="C15" t="n">
-        <v>257839957.849</v>
+        <v>271993731.416</v>
       </c>
       <c r="D15" t="n">
-        <v>117.2036</v>
+        <v>13.7375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B16" t="n">
-        <v>333892.226</v>
+        <v>382769.719</v>
       </c>
       <c r="C16" t="n">
-        <v>282680561.857</v>
+        <v>323530143.714</v>
       </c>
       <c r="D16" t="n">
-        <v>128.4952</v>
+        <v>16.3404</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B17" t="n">
-        <v>376832.796</v>
+        <v>277460.614</v>
       </c>
       <c r="C17" t="n">
-        <v>246883376.828</v>
+        <v>257839957.849</v>
       </c>
       <c r="D17" t="n">
-        <v>112.2232</v>
+        <v>13.0226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B18" t="n">
-        <v>314064.319</v>
+        <v>333892.226</v>
       </c>
       <c r="C18" t="n">
-        <v>279860209.179</v>
+        <v>282680561.857</v>
       </c>
       <c r="D18" t="n">
-        <v>127.2132</v>
+        <v>14.2772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B19" t="n">
-        <v>404250.933</v>
+        <v>376832.796</v>
       </c>
       <c r="C19" t="n">
-        <v>248143546.655</v>
+        <v>246883376.828</v>
       </c>
       <c r="D19" t="n">
-        <v>112.796</v>
+        <v>12.4692</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B20" t="n">
-        <v>318546.705</v>
+        <v>314064.319</v>
       </c>
       <c r="C20" t="n">
-        <v>260599167.781</v>
+        <v>279860209.179</v>
       </c>
       <c r="D20" t="n">
-        <v>118.4579</v>
+        <v>14.1348</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B21" t="n">
-        <v>405919.514</v>
+        <v>404250.933</v>
       </c>
       <c r="C21" t="n">
-        <v>275877181.38</v>
+        <v>248143546.655</v>
       </c>
       <c r="D21" t="n">
-        <v>125.4026</v>
+        <v>12.5329</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B22" t="n">
-        <v>398712.385</v>
+        <v>318546.705</v>
       </c>
       <c r="C22" t="n">
-        <v>243268090.99</v>
+        <v>260599167.781</v>
       </c>
       <c r="D22" t="n">
-        <v>110.5799</v>
+        <v>13.162</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B23" t="n">
-        <v>375274.333</v>
+        <v>405919.514</v>
       </c>
       <c r="C23" t="n">
-        <v>224080808.197</v>
+        <v>275877181.38</v>
       </c>
       <c r="D23" t="n">
-        <v>101.8581</v>
+        <v>13.9336</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B24" t="n">
-        <v>525039.986</v>
+        <v>398712.385</v>
       </c>
       <c r="C24" t="n">
-        <v>317186891.506</v>
+        <v>243268090.99</v>
       </c>
       <c r="D24" t="n">
-        <v>144.1804</v>
+        <v>12.2867</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B25" t="n">
-        <v>587717.714</v>
+        <v>375274.333</v>
       </c>
       <c r="C25" t="n">
-        <v>428093693.481</v>
+        <v>224080808.197</v>
       </c>
       <c r="D25" t="n">
-        <v>194.5941</v>
+        <v>11.3176</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B26" t="n">
-        <v>621508.068</v>
+        <v>525039.986</v>
       </c>
       <c r="C26" t="n">
-        <v>370032906.499</v>
+        <v>317186891.506</v>
       </c>
       <c r="D26" t="n">
-        <v>168.202</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B27" t="n">
-        <v>649048.1</v>
+        <v>587717.714</v>
       </c>
       <c r="C27" t="n">
-        <v>368460094.594</v>
+        <v>428093693.481</v>
       </c>
       <c r="D27" t="n">
-        <v>167.4871</v>
+        <v>21.6216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B28" t="n">
-        <v>591170.513</v>
+        <v>621508.068</v>
       </c>
       <c r="C28" t="n">
-        <v>316183035.803</v>
+        <v>370032906.499</v>
       </c>
       <c r="D28" t="n">
-        <v>143.7241</v>
+        <v>18.6891</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B29" t="n">
-        <v>633452.101</v>
+        <v>649048.1</v>
       </c>
       <c r="C29" t="n">
-        <v>481647446.168</v>
+        <v>368460094.594</v>
       </c>
       <c r="D29" t="n">
-        <v>218.9375</v>
+        <v>18.6097</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B30" t="n">
-        <v>626995.152</v>
+        <v>591170.513</v>
       </c>
       <c r="C30" t="n">
-        <v>501693234.334</v>
+        <v>316183035.803</v>
       </c>
       <c r="D30" t="n">
-        <v>228.0495</v>
+        <v>15.9693</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B31" t="n">
-        <v>612581.657</v>
+        <v>633452.101</v>
       </c>
       <c r="C31" t="n">
-        <v>602008002.199</v>
+        <v>481647446.168</v>
       </c>
       <c r="D31" t="n">
-        <v>273.6486</v>
+        <v>24.3264</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B32" t="n">
-        <v>724339.875</v>
+        <v>626995.152</v>
       </c>
       <c r="C32" t="n">
-        <v>619311256.943</v>
+        <v>501693234.334</v>
       </c>
       <c r="D32" t="n">
-        <v>281.5139</v>
+        <v>25.3388</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B33" t="n">
-        <v>916756.885</v>
+        <v>612581.657</v>
       </c>
       <c r="C33" t="n">
-        <v>765417876.048</v>
+        <v>602008002.199</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9281</v>
+        <v>30.4054</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B34" t="n">
-        <v>805518.4</v>
+        <v>724339.875</v>
       </c>
       <c r="C34" t="n">
-        <v>583491548.433</v>
+        <v>619311256.943</v>
       </c>
       <c r="D34" t="n">
-        <v>265.2317</v>
+        <v>31.2793</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B35" t="n">
-        <v>982308.63</v>
+        <v>916756.885</v>
       </c>
       <c r="C35" t="n">
-        <v>722253732.003</v>
+        <v>765417876.048</v>
       </c>
       <c r="D35" t="n">
-        <v>328.3074</v>
+        <v>38.6587</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B36" t="n">
-        <v>762089.218</v>
+        <v>805518.4</v>
       </c>
       <c r="C36" t="n">
-        <v>468232345.242</v>
+        <v>583491548.433</v>
       </c>
       <c r="D36" t="n">
-        <v>212.8395</v>
+        <v>29.4702</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B37" t="n">
-        <v>753132.893</v>
+        <v>982308.63</v>
       </c>
       <c r="C37" t="n">
-        <v>478036007.163</v>
+        <v>722253732.003</v>
       </c>
       <c r="D37" t="n">
-        <v>217.2959</v>
+        <v>36.4786</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B38" t="n">
-        <v>633185.121</v>
+        <v>762089.218</v>
       </c>
       <c r="C38" t="n">
-        <v>414141601.856</v>
+        <v>468232345.242</v>
       </c>
       <c r="D38" t="n">
-        <v>188.2521</v>
+        <v>23.6488</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B39" t="n">
-        <v>710858.88</v>
+        <v>753132.893</v>
       </c>
       <c r="C39" t="n">
-        <v>472299352.45</v>
+        <v>478036007.163</v>
       </c>
       <c r="D39" t="n">
-        <v>214.6882</v>
+        <v>24.144</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B40" t="n">
-        <v>608719.4399999999</v>
+        <v>633185.121</v>
       </c>
       <c r="C40" t="n">
-        <v>429426057.423</v>
+        <v>414141601.856</v>
       </c>
       <c r="D40" t="n">
-        <v>195.1998</v>
+        <v>20.9169</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B41" t="n">
-        <v>633022.219</v>
+        <v>710858.88</v>
       </c>
       <c r="C41" t="n">
-        <v>419503045.346</v>
+        <v>472299352.45</v>
       </c>
       <c r="D41" t="n">
-        <v>190.6892</v>
+        <v>23.8542</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B42" t="n">
-        <v>614979.312</v>
+        <v>608719.4399999999</v>
       </c>
       <c r="C42" t="n">
-        <v>468254656.793</v>
+        <v>429426057.423</v>
       </c>
       <c r="D42" t="n">
-        <v>212.8497</v>
+        <v>21.6889</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B43" t="n">
-        <v>580198.528</v>
+        <v>633022.219</v>
       </c>
       <c r="C43" t="n">
-        <v>407922139.339</v>
+        <v>419503045.346</v>
       </c>
       <c r="D43" t="n">
-        <v>185.425</v>
+        <v>21.1877</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B44" t="n">
-        <v>763415.6409999999</v>
+        <v>614979.312</v>
       </c>
       <c r="C44" t="n">
-        <v>585774699.314</v>
+        <v>468254656.793</v>
       </c>
       <c r="D44" t="n">
-        <v>266.2696</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B45" t="n">
-        <v>768022.227</v>
+        <v>580198.528</v>
       </c>
       <c r="C45" t="n">
-        <v>508238232.945</v>
+        <v>407922139.339</v>
       </c>
       <c r="D45" t="n">
-        <v>231.0246</v>
+        <v>20.6028</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B46" t="n">
-        <v>899231.28</v>
+        <v>763415.6409999999</v>
       </c>
       <c r="C46" t="n">
-        <v>672953895.449</v>
+        <v>585774699.314</v>
       </c>
       <c r="D46" t="n">
-        <v>305.8977</v>
+        <v>29.5855</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B47" t="n">
-        <v>1047429.741</v>
+        <v>768022.227</v>
       </c>
       <c r="C47" t="n">
-        <v>676704400.513</v>
+        <v>508238232.945</v>
       </c>
       <c r="D47" t="n">
-        <v>307.6025</v>
+        <v>25.6694</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B48" t="n">
-        <v>1153407.853</v>
+        <v>899231.28</v>
       </c>
       <c r="C48" t="n">
-        <v>793463762.244</v>
+        <v>672953895.449</v>
       </c>
       <c r="D48" t="n">
-        <v>360.6766</v>
+        <v>33.9886</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B49" t="n">
-        <v>1274480.615</v>
+        <v>1047429.741</v>
       </c>
       <c r="C49" t="n">
-        <v>875287995.5319999</v>
+        <v>676704400.513</v>
       </c>
       <c r="D49" t="n">
-        <v>397.8706</v>
+        <v>34.1781</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B50" t="n">
-        <v>1481733</v>
+        <v>1153407.853</v>
       </c>
       <c r="C50" t="n">
-        <v>962503312.33</v>
+        <v>793463762.244</v>
       </c>
       <c r="D50" t="n">
-        <v>437.5152</v>
+        <v>40.0752</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B51" t="n">
-        <v>1352368.435</v>
+        <v>1274480.615</v>
       </c>
       <c r="C51" t="n">
-        <v>988875141.302</v>
+        <v>875287995.5319999</v>
       </c>
       <c r="D51" t="n">
-        <v>449.5028</v>
+        <v>44.2078</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B52" t="n">
-        <v>1420684.616</v>
+        <v>1481733</v>
       </c>
       <c r="C52" t="n">
-        <v>1047436124.305</v>
+        <v>962503312.33</v>
       </c>
       <c r="D52" t="n">
-        <v>476.1222</v>
+        <v>48.6128</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B53" t="n">
-        <v>1417655.699</v>
+        <v>1352368.435</v>
       </c>
       <c r="C53" t="n">
-        <v>948360685.273</v>
+        <v>988875141.302</v>
       </c>
       <c r="D53" t="n">
-        <v>431.0865</v>
+        <v>49.9448</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B54" t="n">
-        <v>1144613.534</v>
+        <v>1420684.616</v>
       </c>
       <c r="C54" t="n">
-        <v>1020018123.044</v>
+        <v>1047436124.305</v>
       </c>
       <c r="D54" t="n">
-        <v>463.6591</v>
+        <v>52.9025</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B55" t="n">
-        <v>1215626.232</v>
+        <v>1417655.699</v>
       </c>
       <c r="C55" t="n">
-        <v>915984795.285</v>
+        <v>948360685.273</v>
       </c>
       <c r="D55" t="n">
-        <v>416.3697</v>
+        <v>47.8985</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B56" t="n">
-        <v>1373149.721</v>
+        <v>1144613.534</v>
       </c>
       <c r="C56" t="n">
-        <v>905952237.531</v>
+        <v>1020018123.044</v>
       </c>
       <c r="D56" t="n">
-        <v>411.8094</v>
+        <v>51.5177</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B57" t="n">
-        <v>1215295.862</v>
+        <v>1215626.232</v>
       </c>
       <c r="C57" t="n">
-        <v>953842334.242</v>
+        <v>915984795.285</v>
       </c>
       <c r="D57" t="n">
-        <v>433.5783</v>
+        <v>46.2633</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B58" t="n">
-        <v>1088108.698</v>
+        <v>1373149.721</v>
       </c>
       <c r="C58" t="n">
-        <v>857107094.656</v>
+        <v>905952237.531</v>
       </c>
       <c r="D58" t="n">
-        <v>389.6063</v>
+        <v>45.7566</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B59" t="n">
-        <v>1026235.69</v>
+        <v>1215295.862</v>
       </c>
       <c r="C59" t="n">
-        <v>834954858.0549999</v>
+        <v>953842334.242</v>
       </c>
       <c r="D59" t="n">
-        <v>379.5368</v>
+        <v>48.1754</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B60" t="n">
-        <v>980106.569</v>
+        <v>1088108.698</v>
       </c>
       <c r="C60" t="n">
-        <v>817999066.038</v>
+        <v>857107094.656</v>
       </c>
       <c r="D60" t="n">
-        <v>371.8294</v>
+        <v>43.2896</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B61" t="n">
-        <v>934934.139</v>
+        <v>1026235.69</v>
       </c>
       <c r="C61" t="n">
-        <v>786701307.005</v>
+        <v>834954858.0549999</v>
       </c>
       <c r="D61" t="n">
-        <v>357.6027</v>
+        <v>42.1708</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B62" t="n">
-        <v>867953.165</v>
+        <v>980106.569</v>
       </c>
       <c r="C62" t="n">
-        <v>784696091.215</v>
+        <v>817999066.038</v>
       </c>
       <c r="D62" t="n">
-        <v>356.6912</v>
+        <v>41.3144</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B63" t="n">
-        <v>807049.969</v>
+        <v>934934.139</v>
       </c>
       <c r="C63" t="n">
-        <v>578970183.699</v>
+        <v>786701307.005</v>
       </c>
       <c r="D63" t="n">
-        <v>263.1765</v>
+        <v>39.7336</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B64" t="n">
-        <v>952156.209</v>
+        <v>867953.165</v>
       </c>
       <c r="C64" t="n">
-        <v>811015137.8099999</v>
+        <v>784696091.215</v>
       </c>
       <c r="D64" t="n">
-        <v>368.6548</v>
+        <v>39.6324</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B65" t="n">
-        <v>947754.687</v>
+        <v>807049.969</v>
       </c>
       <c r="C65" t="n">
-        <v>708309380.228</v>
+        <v>578970183.699</v>
       </c>
       <c r="D65" t="n">
-        <v>321.9689</v>
+        <v>29.2418</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B66" t="n">
-        <v>1002911.839</v>
+        <v>952156.209</v>
       </c>
       <c r="C66" t="n">
-        <v>824670414.679</v>
+        <v>811015137.8099999</v>
       </c>
       <c r="D66" t="n">
-        <v>374.8619</v>
+        <v>40.9616</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B67" t="n">
-        <v>1061567.204</v>
+        <v>947754.687</v>
       </c>
       <c r="C67" t="n">
-        <v>914481786.638</v>
+        <v>708309380.228</v>
       </c>
       <c r="D67" t="n">
-        <v>415.6865</v>
+        <v>35.7743</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B68" t="n">
-        <v>1090617.1</v>
+        <v>1002911.839</v>
       </c>
       <c r="C68" t="n">
-        <v>979608520.376</v>
+        <v>824670414.679</v>
       </c>
       <c r="D68" t="n">
-        <v>445.2905</v>
+        <v>41.6513</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B69" t="n">
-        <v>1011802.277</v>
+        <v>1061567.204</v>
       </c>
       <c r="C69" t="n">
-        <v>797581813.398</v>
+        <v>914481786.638</v>
       </c>
       <c r="D69" t="n">
-        <v>362.5485</v>
+        <v>46.1874</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B70" t="n">
-        <v>944193.911</v>
+        <v>1090617.1</v>
       </c>
       <c r="C70" t="n">
-        <v>819134206.8279999</v>
+        <v>979608520.376</v>
       </c>
       <c r="D70" t="n">
-        <v>372.3454</v>
+        <v>49.4767</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B71" t="n">
-        <v>813925.675</v>
+        <v>1011802.277</v>
       </c>
       <c r="C71" t="n">
-        <v>673443411.031</v>
+        <v>797581813.398</v>
       </c>
       <c r="D71" t="n">
-        <v>306.1202</v>
+        <v>40.2832</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B72" t="n">
-        <v>750172.107</v>
+        <v>944193.911</v>
       </c>
       <c r="C72" t="n">
-        <v>638540970.21</v>
+        <v>819134206.8279999</v>
       </c>
       <c r="D72" t="n">
-        <v>290.255</v>
+        <v>41.3717</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B73" t="n">
-        <v>793008.066</v>
+        <v>813925.675</v>
       </c>
       <c r="C73" t="n">
-        <v>660280105.151</v>
+        <v>673443411.031</v>
       </c>
       <c r="D73" t="n">
-        <v>300.1367</v>
+        <v>34.0134</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B74" t="n">
-        <v>927329.015</v>
+        <v>750172.107</v>
       </c>
       <c r="C74" t="n">
-        <v>756777061.326</v>
+        <v>638540970.21</v>
       </c>
       <c r="D74" t="n">
-        <v>344.0003</v>
+        <v>32.2506</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B75" t="n">
-        <v>906827.105</v>
+        <v>793008.066</v>
       </c>
       <c r="C75" t="n">
-        <v>648802579.586</v>
+        <v>660280105.151</v>
       </c>
       <c r="D75" t="n">
-        <v>294.9195</v>
+        <v>33.3485</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B76" t="n">
-        <v>972189.868</v>
+        <v>927329.015</v>
       </c>
       <c r="C76" t="n">
-        <v>907732226.949</v>
+        <v>756777061.326</v>
       </c>
       <c r="D76" t="n">
-        <v>412.6185</v>
+        <v>38.2223</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B77" t="n">
-        <v>956179.983</v>
+        <v>906827.105</v>
       </c>
       <c r="C77" t="n">
-        <v>730001248.069</v>
+        <v>648802579.586</v>
       </c>
       <c r="D77" t="n">
-        <v>331.8291</v>
+        <v>32.7688</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B78" t="n">
-        <v>968801.566</v>
+        <v>972189.868</v>
       </c>
       <c r="C78" t="n">
-        <v>810466436.722</v>
+        <v>907732226.949</v>
       </c>
       <c r="D78" t="n">
-        <v>368.4054</v>
+        <v>45.8465</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B79" t="n">
-        <v>967233.044</v>
+        <v>956179.983</v>
       </c>
       <c r="C79" t="n">
-        <v>738125818.198</v>
+        <v>730001248.069</v>
       </c>
       <c r="D79" t="n">
-        <v>335.5222</v>
+        <v>36.8699</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B80" t="n">
-        <v>1022068.794</v>
+        <v>968801.566</v>
       </c>
       <c r="C80" t="n">
-        <v>925264464.127</v>
+        <v>810466436.722</v>
       </c>
       <c r="D80" t="n">
-        <v>420.5879</v>
+        <v>40.9339</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B81" t="n">
-        <v>1130374.283</v>
+        <v>967233.044</v>
       </c>
       <c r="C81" t="n">
-        <v>820524344.604</v>
+        <v>738125818.198</v>
       </c>
       <c r="D81" t="n">
-        <v>372.9773</v>
+        <v>37.2802</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1022068.794</v>
+      </c>
+      <c r="C82" t="n">
+        <v>925264464.127</v>
+      </c>
+      <c r="D82" t="n">
+        <v>46.732</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1130374.283</v>
+      </c>
+      <c r="C83" t="n">
+        <v>820524344.604</v>
+      </c>
+      <c r="D83" t="n">
+        <v>41.4419</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>2019</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B84" t="n">
         <v>1102866.626</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C84" t="n">
         <v>967218747.553</v>
       </c>
-      <c r="D82" t="n">
-        <v>439.6586</v>
+      <c r="D84" t="n">
+        <v>48.851</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1654,355 +1705,215 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AV1" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AW1" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AX1" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AY1" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AZ1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="BA1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="BB1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BC1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BD1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BE1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BF1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BG1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BH1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BI1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BJ1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BK1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BL1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BM1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BN1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BO1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BP1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BQ1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BR1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BS1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BT1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BU1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BV1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1951</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1952</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1957</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1958</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1959</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1960</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1962</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1964</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1965</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1966</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1967</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>1968</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>1969</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>1972</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AX1" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AY1" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AZ1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="BA1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="BB1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BC1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BD1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BE1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BF1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BG1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BH1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BI1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BJ1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BK1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BL1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BM1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BN1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BO1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BP1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BQ1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BR1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BS1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BT1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BU1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BV1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -53471,6 +53382,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53649,355 +53799,215 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AZ4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BA4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BI4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BJ4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BK4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BL4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BM4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BN4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BO4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BP4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BQ4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BR4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BS4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BT4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1953</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1954</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1955</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1957</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1959</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1963</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1964</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1965</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1966</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1967</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1969</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1970</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1972</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BS4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BT4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -91405,7 +91415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/LME_002/LME_002.xlsx
+++ b/data/LME_002/LME_002.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$73</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,9 +620,6 @@
       <c r="C15" t="n">
         <v>271993731.416</v>
       </c>
-      <c r="D15" t="n">
-        <v>13.7375</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -631,9 +631,6 @@
       <c r="C16" t="n">
         <v>323530143.714</v>
       </c>
-      <c r="D16" t="n">
-        <v>16.3404</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -645,9 +642,6 @@
       <c r="C17" t="n">
         <v>257839957.849</v>
       </c>
-      <c r="D17" t="n">
-        <v>13.0226</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -659,9 +653,6 @@
       <c r="C18" t="n">
         <v>282680561.857</v>
       </c>
-      <c r="D18" t="n">
-        <v>14.2772</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -673,9 +664,6 @@
       <c r="C19" t="n">
         <v>246883376.828</v>
       </c>
-      <c r="D19" t="n">
-        <v>12.4692</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -687,9 +675,6 @@
       <c r="C20" t="n">
         <v>279860209.179</v>
       </c>
-      <c r="D20" t="n">
-        <v>14.1348</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -701,9 +686,6 @@
       <c r="C21" t="n">
         <v>248143546.655</v>
       </c>
-      <c r="D21" t="n">
-        <v>12.5329</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -715,9 +697,6 @@
       <c r="C22" t="n">
         <v>260599167.781</v>
       </c>
-      <c r="D22" t="n">
-        <v>13.162</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -729,9 +708,6 @@
       <c r="C23" t="n">
         <v>275877181.38</v>
       </c>
-      <c r="D23" t="n">
-        <v>13.9336</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -743,9 +719,6 @@
       <c r="C24" t="n">
         <v>243268090.99</v>
       </c>
-      <c r="D24" t="n">
-        <v>12.2867</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -757,9 +730,6 @@
       <c r="C25" t="n">
         <v>224080808.197</v>
       </c>
-      <c r="D25" t="n">
-        <v>11.3176</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -771,9 +741,6 @@
       <c r="C26" t="n">
         <v>317186891.506</v>
       </c>
-      <c r="D26" t="n">
-        <v>16.02</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -785,9 +752,6 @@
       <c r="C27" t="n">
         <v>428093693.481</v>
       </c>
-      <c r="D27" t="n">
-        <v>21.6216</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -799,9 +763,6 @@
       <c r="C28" t="n">
         <v>370032906.499</v>
       </c>
-      <c r="D28" t="n">
-        <v>18.6891</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -813,9 +774,6 @@
       <c r="C29" t="n">
         <v>368460094.594</v>
       </c>
-      <c r="D29" t="n">
-        <v>18.6097</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -827,9 +785,6 @@
       <c r="C30" t="n">
         <v>316183035.803</v>
       </c>
-      <c r="D30" t="n">
-        <v>15.9693</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -841,9 +796,6 @@
       <c r="C31" t="n">
         <v>481647446.168</v>
       </c>
-      <c r="D31" t="n">
-        <v>24.3264</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -855,9 +807,6 @@
       <c r="C32" t="n">
         <v>501693234.334</v>
       </c>
-      <c r="D32" t="n">
-        <v>25.3388</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -869,9 +818,6 @@
       <c r="C33" t="n">
         <v>602008002.199</v>
       </c>
-      <c r="D33" t="n">
-        <v>30.4054</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -883,9 +829,6 @@
       <c r="C34" t="n">
         <v>619311256.943</v>
       </c>
-      <c r="D34" t="n">
-        <v>31.2793</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -897,9 +840,6 @@
       <c r="C35" t="n">
         <v>765417876.048</v>
       </c>
-      <c r="D35" t="n">
-        <v>38.6587</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -911,9 +851,6 @@
       <c r="C36" t="n">
         <v>583491548.433</v>
       </c>
-      <c r="D36" t="n">
-        <v>29.4702</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -925,9 +862,6 @@
       <c r="C37" t="n">
         <v>722253732.003</v>
       </c>
-      <c r="D37" t="n">
-        <v>36.4786</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -939,9 +873,6 @@
       <c r="C38" t="n">
         <v>468232345.242</v>
       </c>
-      <c r="D38" t="n">
-        <v>23.6488</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -953,9 +884,6 @@
       <c r="C39" t="n">
         <v>478036007.163</v>
       </c>
-      <c r="D39" t="n">
-        <v>24.144</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -967,9 +895,6 @@
       <c r="C40" t="n">
         <v>414141601.856</v>
       </c>
-      <c r="D40" t="n">
-        <v>20.9169</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -981,9 +906,6 @@
       <c r="C41" t="n">
         <v>472299352.45</v>
       </c>
-      <c r="D41" t="n">
-        <v>23.8542</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -995,9 +917,6 @@
       <c r="C42" t="n">
         <v>429426057.423</v>
       </c>
-      <c r="D42" t="n">
-        <v>21.6889</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1009,9 +928,6 @@
       <c r="C43" t="n">
         <v>419503045.346</v>
       </c>
-      <c r="D43" t="n">
-        <v>21.1877</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1023,9 +939,6 @@
       <c r="C44" t="n">
         <v>468254656.793</v>
       </c>
-      <c r="D44" t="n">
-        <v>23.65</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1037,9 +950,6 @@
       <c r="C45" t="n">
         <v>407922139.339</v>
       </c>
-      <c r="D45" t="n">
-        <v>20.6028</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1051,9 +961,6 @@
       <c r="C46" t="n">
         <v>585774699.314</v>
       </c>
-      <c r="D46" t="n">
-        <v>29.5855</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1065,9 +972,6 @@
       <c r="C47" t="n">
         <v>508238232.945</v>
       </c>
-      <c r="D47" t="n">
-        <v>25.6694</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1079,9 +983,6 @@
       <c r="C48" t="n">
         <v>672953895.449</v>
       </c>
-      <c r="D48" t="n">
-        <v>33.9886</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1093,9 +994,6 @@
       <c r="C49" t="n">
         <v>676704400.513</v>
       </c>
-      <c r="D49" t="n">
-        <v>34.1781</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1107,9 +1005,6 @@
       <c r="C50" t="n">
         <v>793463762.244</v>
       </c>
-      <c r="D50" t="n">
-        <v>40.0752</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1121,9 +1016,6 @@
       <c r="C51" t="n">
         <v>875287995.5319999</v>
       </c>
-      <c r="D51" t="n">
-        <v>44.2078</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1135,9 +1027,6 @@
       <c r="C52" t="n">
         <v>962503312.33</v>
       </c>
-      <c r="D52" t="n">
-        <v>48.6128</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1149,9 +1038,6 @@
       <c r="C53" t="n">
         <v>988875141.302</v>
       </c>
-      <c r="D53" t="n">
-        <v>49.9448</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1163,9 +1049,6 @@
       <c r="C54" t="n">
         <v>1047436124.305</v>
       </c>
-      <c r="D54" t="n">
-        <v>52.9025</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1177,9 +1060,6 @@
       <c r="C55" t="n">
         <v>948360685.273</v>
       </c>
-      <c r="D55" t="n">
-        <v>47.8985</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1191,9 +1071,6 @@
       <c r="C56" t="n">
         <v>1020018123.044</v>
       </c>
-      <c r="D56" t="n">
-        <v>51.5177</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1205,9 +1082,6 @@
       <c r="C57" t="n">
         <v>915984795.285</v>
       </c>
-      <c r="D57" t="n">
-        <v>46.2633</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1219,9 +1093,6 @@
       <c r="C58" t="n">
         <v>905952237.531</v>
       </c>
-      <c r="D58" t="n">
-        <v>45.7566</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1233,9 +1104,6 @@
       <c r="C59" t="n">
         <v>953842334.242</v>
       </c>
-      <c r="D59" t="n">
-        <v>48.1754</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1247,9 +1115,6 @@
       <c r="C60" t="n">
         <v>857107094.656</v>
       </c>
-      <c r="D60" t="n">
-        <v>43.2896</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1261,9 +1126,6 @@
       <c r="C61" t="n">
         <v>834954858.0549999</v>
       </c>
-      <c r="D61" t="n">
-        <v>42.1708</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1275,9 +1137,6 @@
       <c r="C62" t="n">
         <v>817999066.038</v>
       </c>
-      <c r="D62" t="n">
-        <v>41.3144</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1290,7 +1149,7 @@
         <v>786701307.005</v>
       </c>
       <c r="D63" t="n">
-        <v>39.7336</v>
+        <v>32.1164</v>
       </c>
     </row>
     <row r="64">
@@ -1304,7 +1163,7 @@
         <v>784696091.215</v>
       </c>
       <c r="D64" t="n">
-        <v>39.6324</v>
+        <v>31.9602</v>
       </c>
     </row>
     <row r="65">
@@ -1318,7 +1177,7 @@
         <v>578970183.699</v>
       </c>
       <c r="D65" t="n">
-        <v>29.2418</v>
+        <v>22.7613</v>
       </c>
     </row>
     <row r="66">
@@ -1332,7 +1191,7 @@
         <v>811015137.8099999</v>
       </c>
       <c r="D66" t="n">
-        <v>40.9616</v>
+        <v>32.6358</v>
       </c>
     </row>
     <row r="67">
@@ -1346,7 +1205,7 @@
         <v>708309380.228</v>
       </c>
       <c r="D67" t="n">
-        <v>35.7743</v>
+        <v>27.0695</v>
       </c>
     </row>
     <row r="68">
@@ -1360,7 +1219,7 @@
         <v>824670414.679</v>
       </c>
       <c r="D68" t="n">
-        <v>41.6513</v>
+        <v>31.7661</v>
       </c>
     </row>
     <row r="69">
@@ -1374,7 +1233,7 @@
         <v>914481786.638</v>
       </c>
       <c r="D69" t="n">
-        <v>46.1874</v>
+        <v>36.8787</v>
       </c>
     </row>
     <row r="70">
@@ -1388,7 +1247,7 @@
         <v>979608520.376</v>
       </c>
       <c r="D70" t="n">
-        <v>49.4767</v>
+        <v>40.1703</v>
       </c>
     </row>
     <row r="71">
@@ -1402,7 +1261,7 @@
         <v>797581813.398</v>
       </c>
       <c r="D71" t="n">
-        <v>40.2832</v>
+        <v>33.0012</v>
       </c>
     </row>
     <row r="72">
@@ -1416,7 +1275,7 @@
         <v>819134206.8279999</v>
       </c>
       <c r="D72" t="n">
-        <v>41.3717</v>
+        <v>32.7022</v>
       </c>
     </row>
     <row r="73">
@@ -1430,7 +1289,7 @@
         <v>673443411.031</v>
       </c>
       <c r="D73" t="n">
-        <v>34.0134</v>
+        <v>28.1744</v>
       </c>
     </row>
     <row r="74">
@@ -1444,7 +1303,7 @@
         <v>638540970.21</v>
       </c>
       <c r="D74" t="n">
-        <v>32.2506</v>
+        <v>25.5548</v>
       </c>
     </row>
     <row r="75">
@@ -1458,7 +1317,7 @@
         <v>660280105.151</v>
       </c>
       <c r="D75" t="n">
-        <v>33.3485</v>
+        <v>27.3329</v>
       </c>
     </row>
     <row r="76">
@@ -1472,7 +1331,7 @@
         <v>756777061.326</v>
       </c>
       <c r="D76" t="n">
-        <v>38.2223</v>
+        <v>29.931</v>
       </c>
     </row>
     <row r="77">
@@ -1486,7 +1345,7 @@
         <v>648802579.586</v>
       </c>
       <c r="D77" t="n">
-        <v>32.7688</v>
+        <v>26.8083</v>
       </c>
     </row>
     <row r="78">
@@ -1500,7 +1359,7 @@
         <v>907732226.949</v>
       </c>
       <c r="D78" t="n">
-        <v>45.8465</v>
+        <v>36.1788</v>
       </c>
     </row>
     <row r="79">
@@ -1514,7 +1373,7 @@
         <v>730001248.069</v>
       </c>
       <c r="D79" t="n">
-        <v>36.8699</v>
+        <v>27.3455</v>
       </c>
     </row>
     <row r="80">
@@ -1528,7 +1387,7 @@
         <v>810466436.722</v>
       </c>
       <c r="D80" t="n">
-        <v>40.9339</v>
+        <v>32.5765</v>
       </c>
     </row>
     <row r="81">
@@ -1542,7 +1401,7 @@
         <v>738125818.198</v>
       </c>
       <c r="D81" t="n">
-        <v>37.2802</v>
+        <v>30.5982</v>
       </c>
     </row>
     <row r="82">
@@ -1556,7 +1415,7 @@
         <v>925264464.127</v>
       </c>
       <c r="D82" t="n">
-        <v>46.732</v>
+        <v>40.6072</v>
       </c>
     </row>
     <row r="83">
@@ -1570,7 +1429,7 @@
         <v>820524344.604</v>
       </c>
       <c r="D83" t="n">
-        <v>41.4419</v>
+        <v>34.5884</v>
       </c>
     </row>
     <row r="84">
@@ -1584,17 +1443,2281 @@
         <v>967218747.553</v>
       </c>
       <c r="D84" t="n">
-        <v>48.851</v>
+        <v>40.4238</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1950</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1951</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1952</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1955</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1957</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1958</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1959</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1960</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1961</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1963</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1964</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1965</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1966</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1967</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1970</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1971</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1972</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1973</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1977</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1979</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1983</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1984</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1986</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1990</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B52" t="n">
+        <v>272170180.0748689</v>
+      </c>
+      <c r="G52" t="n">
+        <v>272170180.0748689</v>
+      </c>
+      <c r="H52" t="n">
+        <v>272170180.0748689</v>
+      </c>
+      <c r="I52" t="n">
+        <v>272170180.0748689</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B53" t="n">
+        <v>272803168.238763</v>
+      </c>
+      <c r="G53" t="n">
+        <v>272803168.238763</v>
+      </c>
+      <c r="H53" t="n">
+        <v>272803168.238763</v>
+      </c>
+      <c r="I53" t="n">
+        <v>272803168.238763</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B54" t="n">
+        <v>282628490.9387029</v>
+      </c>
+      <c r="G54" t="n">
+        <v>282628490.9387029</v>
+      </c>
+      <c r="H54" t="n">
+        <v>282628490.9387029</v>
+      </c>
+      <c r="I54" t="n">
+        <v>282628490.9387029</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B55" t="n">
+        <v>276116786.2583745</v>
+      </c>
+      <c r="G55" t="n">
+        <v>276116786.2583745</v>
+      </c>
+      <c r="H55" t="n">
+        <v>276116786.2583745</v>
+      </c>
+      <c r="I55" t="n">
+        <v>276116786.2583745</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B56" t="n">
+        <v>290736763.1281791</v>
+      </c>
+      <c r="G56" t="n">
+        <v>290736763.1281791</v>
+      </c>
+      <c r="H56" t="n">
+        <v>290736763.1281791</v>
+      </c>
+      <c r="I56" t="n">
+        <v>290736763.1281791</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B57" t="n">
+        <v>288452403.3075644</v>
+      </c>
+      <c r="C57" t="n">
+        <v>394314973.213361</v>
+      </c>
+      <c r="D57" t="n">
+        <v>260986483.0273755</v>
+      </c>
+      <c r="E57" t="n">
+        <v>362116010.2561631</v>
+      </c>
+      <c r="F57" t="n">
+        <v>280016957.59654</v>
+      </c>
+      <c r="G57" t="n">
+        <v>288452403.3075644</v>
+      </c>
+      <c r="H57" t="n">
+        <v>260986483.0273755</v>
+      </c>
+      <c r="I57" t="n">
+        <v>394314973.213361</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>5</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B58" t="n">
+        <v>275522586.0977544</v>
+      </c>
+      <c r="C58" t="n">
+        <v>383114169.9860178</v>
+      </c>
+      <c r="D58" t="n">
+        <v>251358356.0917511</v>
+      </c>
+      <c r="E58" t="n">
+        <v>340514840.7172722</v>
+      </c>
+      <c r="F58" t="n">
+        <v>258763379.9441097</v>
+      </c>
+      <c r="G58" t="n">
+        <v>275522586.0977544</v>
+      </c>
+      <c r="H58" t="n">
+        <v>251358356.0917511</v>
+      </c>
+      <c r="I58" t="n">
+        <v>383114169.9860178</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B59" t="n">
+        <v>270959559.0153556</v>
+      </c>
+      <c r="C59" t="n">
+        <v>371912602.3396839</v>
+      </c>
+      <c r="D59" t="n">
+        <v>242979589.6194256</v>
+      </c>
+      <c r="E59" t="n">
+        <v>333063031.5536307</v>
+      </c>
+      <c r="F59" t="n">
+        <v>253929090.4620108</v>
+      </c>
+      <c r="G59" t="n">
+        <v>270959559.0153556</v>
+      </c>
+      <c r="H59" t="n">
+        <v>242979589.6194256</v>
+      </c>
+      <c r="I59" t="n">
+        <v>371912602.3396839</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>5</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B60" t="n">
+        <v>268536276.4388743</v>
+      </c>
+      <c r="C60" t="n">
+        <v>356159876.6705213</v>
+      </c>
+      <c r="D60" t="n">
+        <v>235696850.6202291</v>
+      </c>
+      <c r="E60" t="n">
+        <v>318510533.7094649</v>
+      </c>
+      <c r="F60" t="n">
+        <v>255997044.7876002</v>
+      </c>
+      <c r="G60" t="n">
+        <v>268536276.4388743</v>
+      </c>
+      <c r="H60" t="n">
+        <v>235696850.6202291</v>
+      </c>
+      <c r="I60" t="n">
+        <v>356159876.6705213</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>5</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B61" t="n">
+        <v>273402405.0517273</v>
+      </c>
+      <c r="C61" t="n">
+        <v>358536994.5254242</v>
+      </c>
+      <c r="D61" t="n">
+        <v>238121848.1779193</v>
+      </c>
+      <c r="E61" t="n">
+        <v>326603474.2616252</v>
+      </c>
+      <c r="F61" t="n">
+        <v>278314225.2073584</v>
+      </c>
+      <c r="G61" t="n">
+        <v>278314225.2073584</v>
+      </c>
+      <c r="H61" t="n">
+        <v>238121848.1779193</v>
+      </c>
+      <c r="I61" t="n">
+        <v>358536994.5254242</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>5</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B62" t="n">
+        <v>263342097.3051229</v>
+      </c>
+      <c r="C62" t="n">
+        <v>340766659.2754625</v>
+      </c>
+      <c r="D62" t="n">
+        <v>227496445.3442541</v>
+      </c>
+      <c r="E62" t="n">
+        <v>317338063.5380024</v>
+      </c>
+      <c r="F62" t="n">
+        <v>265585203.6369395</v>
+      </c>
+      <c r="G62" t="n">
+        <v>265585203.6369395</v>
+      </c>
+      <c r="H62" t="n">
+        <v>227496445.3442541</v>
+      </c>
+      <c r="I62" t="n">
+        <v>340766659.2754625</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B63" t="n">
+        <v>277634245.4224896</v>
+      </c>
+      <c r="C63" t="n">
+        <v>369228657.6488363</v>
+      </c>
+      <c r="D63" t="n">
+        <v>246749126.9669836</v>
+      </c>
+      <c r="E63" t="n">
+        <v>331432379.71038</v>
+      </c>
+      <c r="F63" t="n">
+        <v>260566584.3161246</v>
+      </c>
+      <c r="G63" t="n">
+        <v>277634245.4224896</v>
+      </c>
+      <c r="H63" t="n">
+        <v>246749126.9669836</v>
+      </c>
+      <c r="I63" t="n">
+        <v>369228657.6488363</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>5</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B64" t="n">
+        <v>261681342.4414569</v>
+      </c>
+      <c r="C64" t="n">
+        <v>344598502.576099</v>
+      </c>
+      <c r="D64" t="n">
+        <v>227558618.7195624</v>
+      </c>
+      <c r="E64" t="n">
+        <v>330334271.0392799</v>
+      </c>
+      <c r="F64" t="n">
+        <v>268411258.6299441</v>
+      </c>
+      <c r="G64" t="n">
+        <v>268411258.6299441</v>
+      </c>
+      <c r="H64" t="n">
+        <v>227558618.7195624</v>
+      </c>
+      <c r="I64" t="n">
+        <v>344598502.576099</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>5</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B65" t="n">
+        <v>266377333.0527477</v>
+      </c>
+      <c r="C65" t="n">
+        <v>354891460.7064647</v>
+      </c>
+      <c r="D65" t="n">
+        <v>235811956.6592389</v>
+      </c>
+      <c r="E65" t="n">
+        <v>341316187.9137331</v>
+      </c>
+      <c r="F65" t="n">
+        <v>280933942.0526852</v>
+      </c>
+      <c r="G65" t="n">
+        <v>280933942.0526852</v>
+      </c>
+      <c r="H65" t="n">
+        <v>235811956.6592389</v>
+      </c>
+      <c r="I65" t="n">
+        <v>354891460.7064647</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B66" t="n">
+        <v>254564388.0699241</v>
+      </c>
+      <c r="C66" t="n">
+        <v>346757851.4283419</v>
+      </c>
+      <c r="D66" t="n">
+        <v>230750120.6816882</v>
+      </c>
+      <c r="E66" t="n">
+        <v>321936074.4580215</v>
+      </c>
+      <c r="F66" t="n">
+        <v>268905681.9063088</v>
+      </c>
+      <c r="G66" t="n">
+        <v>268905681.9063088</v>
+      </c>
+      <c r="H66" t="n">
+        <v>230750120.6816882</v>
+      </c>
+      <c r="I66" t="n">
+        <v>346757851.4283419</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>5</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B67" t="n">
+        <v>278779849.5578514</v>
+      </c>
+      <c r="C67" t="n">
+        <v>395497814.0599619</v>
+      </c>
+      <c r="D67" t="n">
+        <v>263164430.5942551</v>
+      </c>
+      <c r="E67" t="n">
+        <v>352269330.4455253</v>
+      </c>
+      <c r="F67" t="n">
+        <v>272337565.6916948</v>
+      </c>
+      <c r="G67" t="n">
+        <v>278779849.5578514</v>
+      </c>
+      <c r="H67" t="n">
+        <v>263164430.5942551</v>
+      </c>
+      <c r="I67" t="n">
+        <v>395497814.0599619</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>5</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B68" t="n">
+        <v>296616496.7168583</v>
+      </c>
+      <c r="C68" t="n">
+        <v>421875271.3249946</v>
+      </c>
+      <c r="D68" t="n">
+        <v>279834909.1946605</v>
+      </c>
+      <c r="E68" t="n">
+        <v>374362681.0232511</v>
+      </c>
+      <c r="F68" t="n">
+        <v>287316675.3422932</v>
+      </c>
+      <c r="G68" t="n">
+        <v>296616496.7168583</v>
+      </c>
+      <c r="H68" t="n">
+        <v>279834909.1946605</v>
+      </c>
+      <c r="I68" t="n">
+        <v>421875271.3249946</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B69" t="n">
+        <v>276431875.5964727</v>
+      </c>
+      <c r="C69" t="n">
+        <v>395822665.5960488</v>
+      </c>
+      <c r="D69" t="n">
+        <v>259605344.4625155</v>
+      </c>
+      <c r="E69" t="n">
+        <v>341695854.1724866</v>
+      </c>
+      <c r="F69" t="n">
+        <v>245663861.214786</v>
+      </c>
+      <c r="G69" t="n">
+        <v>276431875.5964727</v>
+      </c>
+      <c r="H69" t="n">
+        <v>245663861.214786</v>
+      </c>
+      <c r="I69" t="n">
+        <v>395822665.5960488</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>5</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B70" t="n">
+        <v>268035670.0766088</v>
+      </c>
+      <c r="C70" t="n">
+        <v>393649537.4501468</v>
+      </c>
+      <c r="D70" t="n">
+        <v>257061436.6837432</v>
+      </c>
+      <c r="E70" t="n">
+        <v>358364636.9152854</v>
+      </c>
+      <c r="F70" t="n">
+        <v>247885297.5167673</v>
+      </c>
+      <c r="G70" t="n">
+        <v>268035670.0766088</v>
+      </c>
+      <c r="H70" t="n">
+        <v>247885297.5167673</v>
+      </c>
+      <c r="I70" t="n">
+        <v>393649537.4501468</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B71" t="n">
+        <v>253174788.1003167</v>
+      </c>
+      <c r="C71" t="n">
+        <v>361010433.2777364</v>
+      </c>
+      <c r="D71" t="n">
+        <v>237556950.1990784</v>
+      </c>
+      <c r="E71" t="n">
+        <v>344560194.3830997</v>
+      </c>
+      <c r="F71" t="n">
+        <v>252821085.9555485</v>
+      </c>
+      <c r="G71" t="n">
+        <v>253174788.1003167</v>
+      </c>
+      <c r="H71" t="n">
+        <v>237556950.1990784</v>
+      </c>
+      <c r="I71" t="n">
+        <v>361010433.2777364</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B72" t="n">
+        <v>263583791.9041115</v>
+      </c>
+      <c r="C72" t="n">
+        <v>382068633.7253921</v>
+      </c>
+      <c r="D72" t="n">
+        <v>251921814.5248599</v>
+      </c>
+      <c r="E72" t="n">
+        <v>340261638.6149882</v>
+      </c>
+      <c r="F72" t="n">
+        <v>253825768.9748913</v>
+      </c>
+      <c r="G72" t="n">
+        <v>263583791.9041115</v>
+      </c>
+      <c r="H72" t="n">
+        <v>251921814.5248599</v>
+      </c>
+      <c r="I72" t="n">
+        <v>382068633.7253921</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>5</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B73" t="n">
+        <v>265855268.3667683</v>
+      </c>
+      <c r="C73" t="n">
+        <v>400305706.2019643</v>
+      </c>
+      <c r="D73" t="n">
+        <v>263697730.5170404</v>
+      </c>
+      <c r="E73" t="n">
+        <v>374996972.3475495</v>
+      </c>
+      <c r="F73" t="n">
+        <v>255890596.8752764</v>
+      </c>
+      <c r="G73" t="n">
+        <v>265855268.3667683</v>
+      </c>
+      <c r="H73" t="n">
+        <v>255890596.8752764</v>
+      </c>
+      <c r="I73" t="n">
+        <v>400305706.2019643</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -51111,2268 +53234,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for LME_002</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Notorynchus cepedianus</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4786.300923</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alopias vulpinus</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Paralichthys californicus</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Isurus oxyrinchus</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lamnidae</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Oncorhynchus gorbuscha</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3090.295433</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Hexanchus griseus</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3019.95172</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Thunnus albacares</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2570.395783</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Oncorhynchus tshawytscha</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2511.886432</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Salvelinus malma</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2511.886432</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Reinhardtius hippoglossoides</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2398.832919</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sebastes melanops</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2398.832919</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Merluccius productus</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2238.721139</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Prionace glauca</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2238.721139</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Galeorhinus galeus</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2187.761624</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Thunnus</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2187.761624</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Ophiodon elongatus</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2089.296131</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Thunnus alalunga</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1995.262315</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Atheresthes evermanni</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1995.262315</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Scombridae</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1819.700859</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Eptatretus stoutii</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1737.800829</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Oncorhynchus kisutch</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1659.586907</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Lampris guttatus</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1659.586907</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Atheresthes stomias</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1479.108388</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Gadus macrocephalus</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1445.439771</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sebastes flavidus</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1412.537545</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Hippoglossus stenolepis</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1380.384265</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Teuthida</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1348.962883</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Eleginus gracilis</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1258.925412</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Oncorhynchus mykiss</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1202.264435</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Psettichthys melanostictus</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1148.153621</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Paralichthyidae</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1148.153621</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Eopsetta jordani</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1122.018454</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Elasmobranchii</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1122.018454</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Thunnus orientalis</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1122.018454</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Sebastes auriculatus</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1071.519305</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Alepisaurus ferox</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1071.519305</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Scomberesocidae</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1023.292992</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Metacarcinus magister</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Chondrichthyes</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Petromyzontidae</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Scyliorhinidae</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="C46" t="n">
-        <v>933.2543010000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Oncorhynchus</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="C47" t="n">
-        <v>891.250938</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Loliginidae</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="C48" t="n">
-        <v>794.3282349999999</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Sebastes reedi</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="C49" t="n">
-        <v>758.577575</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Doryteuthis opalescens</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="C50" t="n">
-        <v>724.43596</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pleuronichthys decurrens</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="C51" t="n">
-        <v>707.945784</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Anoplopoma fimbria</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="C52" t="n">
-        <v>691.830971</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Gadidae</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="C53" t="n">
-        <v>691.830971</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Rajidae</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="C54" t="n">
-        <v>660.693448</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Squalus suckleyi</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="C55" t="n">
-        <v>660.693448</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Sebastes babcocki</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="C56" t="n">
-        <v>660.693448</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Cottidae</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="C57" t="n">
-        <v>645.654229</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Sebastes proriger</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="C58" t="n">
-        <v>645.654229</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Cephalopoda</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="C59" t="n">
-        <v>645.654229</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Sebastes pinniger</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C60" t="n">
-        <v>630.957344</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Raja</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C61" t="n">
-        <v>630.957344</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Sebastes</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="C62" t="n">
-        <v>616.595002</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Coregonus laurettae</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="C63" t="n">
-        <v>616.595002</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Scorpaeniformes</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="C64" t="n">
-        <v>602.559586</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Cancer antennarius</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="C65" t="n">
-        <v>588.843655</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Sciaenidae</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="C66" t="n">
-        <v>575.439937</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Oncorhynchus keta</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="C67" t="n">
-        <v>549.540874</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Sebastidae</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="C68" t="n">
-        <v>549.540874</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Hexagrammidae</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="C69" t="n">
-        <v>524.80746</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Sebastes entomelas</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C70" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Sebastes crameri</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C71" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Sebastes zacentrus</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C72" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Caulolatilus princeps</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C73" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sebastes elongatus</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C74" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sebastes saxicola</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C75" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Sebastes helvomaculatus</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C76" t="n">
-        <v>501.187234</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Hydrolagus colliei</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="C77" t="n">
-        <v>478.630092</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Sebastes rosaceus</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="C78" t="n">
-        <v>478.630092</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sebastes aurora</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="C79" t="n">
-        <v>478.630092</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Mola mola</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="C80" t="n">
-        <v>478.630092</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Hippoglossoides elassodon</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="C81" t="n">
-        <v>467.735141</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Hexagrammos lagocephalus</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="C82" t="n">
-        <v>467.735141</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Caliraja stellulata</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="C83" t="n">
-        <v>426.579519</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sebastolobus alascanus</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="C84" t="n">
-        <v>416.869383</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Scorpaenichthys marmoratus</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="C85" t="n">
-        <v>416.869383</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Stromateidae</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="C86" t="n">
-        <v>416.869383</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C87" t="n">
-        <v>407.380278</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Pleuronectes quadrituberculatus</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="C88" t="n">
-        <v>389.045145</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Octopodidae</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="C89" t="n">
-        <v>389.045145</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Microgadus proximus</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C90" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Platichthys stellatus</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C91" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Apristurus brunneus</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C92" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Octopoda</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C93" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Gadus chalcogrammus</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="C94" t="n">
-        <v>371.535229</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Pleuronectiformes</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="C95" t="n">
-        <v>371.535229</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Trachurus symmetricus</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="C96" t="n">
-        <v>371.535229</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Oncorhynchus nerka</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="C97" t="n">
-        <v>346.73685</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Chionoecetes opilio</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="C98" t="n">
-        <v>346.73685</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Perciformes</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="C99" t="n">
-        <v>338.844156</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Hemilepidotus hemilepidotus</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="C100" t="n">
-        <v>338.844156</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sebastes aleutianus</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="C101" t="n">
-        <v>331.131121</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Sebastes nigrocinctus</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="C102" t="n">
-        <v>331.131121</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Sebastes paucispinis</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="C103" t="n">
-        <v>323.593657</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Anarrhichthys ocellatus</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="C104" t="n">
-        <v>323.593657</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Hyperprosopon argenteum</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C105" t="n">
-        <v>316.227766</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Limanda aspera</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="C106" t="n">
-        <v>309.029543</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Pleuronectidae</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="C107" t="n">
-        <v>309.029543</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Sebastes alutus</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="C108" t="n">
-        <v>301.995172</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Alosa sapidissima</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="C109" t="n">
-        <v>301.995172</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Citharichthys sordidus</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="C110" t="n">
-        <v>288.40315</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Osmeridae</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="C111" t="n">
-        <v>288.40315</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Sebastes goodei</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="C112" t="n">
-        <v>288.40315</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Decapoda</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="C113" t="n">
-        <v>269.15348</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Genyonemus lineatus</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="C114" t="n">
-        <v>269.15348</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Hypomesus pretiosus</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="C115" t="n">
-        <v>269.15348</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Parophrys vetulus</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="C116" t="n">
-        <v>245.470892</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Pleurogrammus monopterygius</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="C117" t="n">
-        <v>239.883292</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Scomber japonicus</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="C118" t="n">
-        <v>239.883292</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Amphistichus rhodoterus</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="C119" t="n">
-        <v>234.422882</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Amphistichus koelzi</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="C120" t="n">
-        <v>229.086765</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Enophrys bison</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="C121" t="n">
-        <v>218.776162</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Enteroctopus dofleini</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="C122" t="n">
-        <v>213.796209</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Penaeidae</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="C123" t="n">
-        <v>204.173794</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Embiotoca lateralis</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="C124" t="n">
-        <v>204.173794</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Coregonus pidschian</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="C125" t="n">
-        <v>204.173794</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Cancer productus</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C126" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Salmonidae</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C127" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Hyperprosopon ellipticum</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C128" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Coregonus</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C129" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Allosmerus elongatus</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C130" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Phanerodon furcatus</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C131" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C132" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Glyptocephalus zachirus</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C133" t="n">
-        <v>177.827941</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Thaleichthys pacificus</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C134" t="n">
-        <v>177.827941</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Dendrobranchiata</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="C135" t="n">
-        <v>173.780083</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Pandalus jordani</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="C136" t="n">
-        <v>169.824365</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Marine groundfishes not identified</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C137" t="n">
-        <v>165.958691</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Microstomus pacificus</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C138" t="n">
-        <v>165.958691</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Atractoscion nobilis</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="C139" t="n">
-        <v>162.18101</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Sebastes jordani</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C140" t="n">
-        <v>158.489319</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Microstomus bathybius</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C141" t="n">
-        <v>158.489319</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Lepidopsetta bilineata</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="C142" t="n">
-        <v>151.356125</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Clupea pallasii</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>144.543977</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Mallotus villosus</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="C144" t="n">
-        <v>141.253754</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Ammodytidae</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="C145" t="n">
-        <v>128.824955</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Chionoecetes bairdi</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="C146" t="n">
-        <v>120.226443</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Gastropoda</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="C147" t="n">
-        <v>114.815362</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Engraulis mordax</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="C148" t="n">
-        <v>93.32543</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Sardinops sagax</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="C149" t="n">
-        <v>69.183097</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Paralithodes</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C150" t="n">
-        <v>66.069345</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Lithodidae</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C151" t="n">
-        <v>66.069345</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Miscellaneous marine crustaceans</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C152" t="n">
-        <v>50.118723</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Pandalidae</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C153" t="n">
-        <v>50.118723</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Pandalus</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C154" t="n">
-        <v>39.810717</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Erimacrus isenbeckii</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C155" t="n">
-        <v>39.810717</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Brachyura</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C156" t="n">
-        <v>39.810717</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Miscellaneous aquatic invertebrates</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="C157" t="n">
-        <v>26.915348</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Mesocentrotus franciscanus</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C158" t="n">
-        <v>25.118864</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Mya arenaria</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="C159" t="n">
-        <v>20.417379</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Strongylocentrotus droebachiensis</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C160" t="n">
-        <v>19.952623</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Chionoecetes</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C161" t="n">
-        <v>19.952623</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Bivalvia</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="C162" t="n">
-        <v>16.982437</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Strongylocentrotus</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C163" t="n">
-        <v>12.589254</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Leukoma staminea</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C164" t="n">
-        <v>12.589254</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Clinocardium nuttallii</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C165" t="n">
-        <v>11.220185</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Tresus</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="C166" t="n">
-        <v>10.715193</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Panopea generosa</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>2</v>
-      </c>
-      <c r="C167" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Siliqua patula</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>2</v>
-      </c>
-      <c r="C168" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Veneridae</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>2</v>
-      </c>
-      <c r="C169" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Saxidomus gigantea</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>2</v>
-      </c>
-      <c r="C170" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Cardiidae</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>2</v>
-      </c>
-      <c r="C171" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Magallana gigas</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>2</v>
-      </c>
-      <c r="C172" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Crassostrea</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>2</v>
-      </c>
-      <c r="C173" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Haliotis</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>2</v>
-      </c>
-      <c r="C174" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -53387,43 +53265,2268 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for LME_002</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Notorynchus cepedianus</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4786.300923</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alopias vulpinus</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Paralichthys californicus</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Isurus oxyrinchus</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lamnidae</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Oncorhynchus gorbuscha</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3090.295433</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hexanchus griseus</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3019.95172</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thunnus albacares</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2570.395783</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Oncorhynchus tshawytscha</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2511.886432</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Salvelinus malma</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2511.886432</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Reinhardtius hippoglossoides</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2398.832919</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sebastes melanops</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2398.832919</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Merluccius productus</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2238.721139</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Prionace glauca</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2238.721139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Galeorhinus galeus</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2187.761624</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Thunnus</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2187.761624</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ophiodon elongatus</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2089.296131</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Thunnus alalunga</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1995.262315</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Atheresthes evermanni</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1995.262315</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1819.700859</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Eptatretus stoutii</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1737.800829</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Oncorhynchus kisutch</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1659.586907</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lampris guttatus</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1659.586907</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Atheresthes stomias</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1479.108388</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gadus macrocephalus</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1445.439771</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sebastes flavidus</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1412.537545</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hippoglossus stenolepis</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1380.384265</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Teuthida</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1348.962883</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Eleginus gracilis</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1258.925412</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Oncorhynchus mykiss</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1202.264435</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Psettichthys melanostictus</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1148.153621</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Paralichthyidae</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1148.153621</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Eopsetta jordani</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1122.018454</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Elasmobranchii</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1122.018454</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Thunnus orientalis</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1122.018454</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sebastes auriculatus</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1071.519305</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Alepisaurus ferox</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1071.519305</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Scomberesocidae</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1023.292992</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Metacarcinus magister</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chondrichthyes</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Petromyzontidae</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Scyliorhinidae</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="C46" t="n">
+        <v>933.2543010000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Oncorhynchus</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="C47" t="n">
+        <v>891.250938</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Loliginidae</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>794.3282349999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sebastes reedi</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="C49" t="n">
+        <v>758.577575</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Doryteuthis opalescens</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="C50" t="n">
+        <v>724.43596</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Pleuronichthys decurrens</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="C51" t="n">
+        <v>707.945784</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Anoplopoma fimbria</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="C52" t="n">
+        <v>691.830971</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gadidae</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="C53" t="n">
+        <v>691.830971</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Rajidae</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C54" t="n">
+        <v>660.693448</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Squalus suckleyi</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C55" t="n">
+        <v>660.693448</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sebastes babcocki</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C56" t="n">
+        <v>660.693448</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Cottidae</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="C57" t="n">
+        <v>645.654229</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sebastes proriger</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="C58" t="n">
+        <v>645.654229</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cephalopoda</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="C59" t="n">
+        <v>645.654229</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sebastes pinniger</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C60" t="n">
+        <v>630.957344</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Raja</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C61" t="n">
+        <v>630.957344</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sebastes</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="C62" t="n">
+        <v>616.595002</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Coregonus laurettae</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="C63" t="n">
+        <v>616.595002</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Scorpaeniformes</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="C64" t="n">
+        <v>602.559586</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cancer antennarius</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="C65" t="n">
+        <v>588.843655</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sciaenidae</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="C66" t="n">
+        <v>575.439937</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Oncorhynchus keta</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="C67" t="n">
+        <v>549.540874</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sebastidae</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="C68" t="n">
+        <v>549.540874</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hexagrammidae</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="C69" t="n">
+        <v>524.80746</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sebastes entomelas</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C70" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sebastes crameri</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C71" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sebastes zacentrus</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C72" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Caulolatilus princeps</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C73" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sebastes elongatus</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C74" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sebastes saxicola</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C75" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sebastes helvomaculatus</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C76" t="n">
+        <v>501.187234</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Hydrolagus colliei</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="C77" t="n">
+        <v>478.630092</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sebastes rosaceus</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="C78" t="n">
+        <v>478.630092</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sebastes aurora</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="C79" t="n">
+        <v>478.630092</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Mola mola</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="C80" t="n">
+        <v>478.630092</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Hippoglossoides elassodon</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="C81" t="n">
+        <v>467.735141</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Hexagrammos lagocephalus</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="C82" t="n">
+        <v>467.735141</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Caliraja stellulata</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="C83" t="n">
+        <v>426.579519</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sebastolobus alascanus</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C84" t="n">
+        <v>416.869383</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Scorpaenichthys marmoratus</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C85" t="n">
+        <v>416.869383</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Stromateidae</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C86" t="n">
+        <v>416.869383</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C87" t="n">
+        <v>407.380278</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Pleuronectes quadrituberculatus</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="C88" t="n">
+        <v>389.045145</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Octopodidae</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="C89" t="n">
+        <v>389.045145</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Microgadus proximus</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C90" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Platichthys stellatus</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C91" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Apristurus brunneus</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C92" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Octopoda</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C93" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Gadus chalcogrammus</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="C94" t="n">
+        <v>371.535229</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Pleuronectiformes</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="C95" t="n">
+        <v>371.535229</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Trachurus symmetricus</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="C96" t="n">
+        <v>371.535229</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Oncorhynchus nerka</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="C97" t="n">
+        <v>346.73685</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Chionoecetes opilio</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="C98" t="n">
+        <v>346.73685</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C99" t="n">
+        <v>338.844156</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Hemilepidotus hemilepidotus</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C100" t="n">
+        <v>338.844156</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sebastes aleutianus</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C101" t="n">
+        <v>331.131121</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sebastes nigrocinctus</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C102" t="n">
+        <v>331.131121</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sebastes paucispinis</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="C103" t="n">
+        <v>323.593657</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Anarrhichthys ocellatus</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="C104" t="n">
+        <v>323.593657</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Hyperprosopon argenteum</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C105" t="n">
+        <v>316.227766</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Limanda aspera</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="C106" t="n">
+        <v>309.029543</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Pleuronectidae</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="C107" t="n">
+        <v>309.029543</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sebastes alutus</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="C108" t="n">
+        <v>301.995172</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Alosa sapidissima</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="C109" t="n">
+        <v>301.995172</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Citharichthys sordidus</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="C110" t="n">
+        <v>288.40315</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Osmeridae</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="C111" t="n">
+        <v>288.40315</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sebastes goodei</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="C112" t="n">
+        <v>288.40315</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Decapoda</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C113" t="n">
+        <v>269.15348</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Genyonemus lineatus</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C114" t="n">
+        <v>269.15348</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Hypomesus pretiosus</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C115" t="n">
+        <v>269.15348</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Parophrys vetulus</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C116" t="n">
+        <v>245.470892</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Pleurogrammus monopterygius</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="C117" t="n">
+        <v>239.883292</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Scomber japonicus</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="C118" t="n">
+        <v>239.883292</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Amphistichus rhodoterus</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="C119" t="n">
+        <v>234.422882</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Amphistichus koelzi</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="C120" t="n">
+        <v>229.086765</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Enophrys bison</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="C121" t="n">
+        <v>218.776162</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Enteroctopus dofleini</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="C122" t="n">
+        <v>213.796209</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Penaeidae</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="C123" t="n">
+        <v>204.173794</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Embiotoca lateralis</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="C124" t="n">
+        <v>204.173794</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Coregonus pidschian</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="C125" t="n">
+        <v>204.173794</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Cancer productus</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C126" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Salmonidae</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C127" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Hyperprosopon ellipticum</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C128" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Coregonus</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C129" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Allosmerus elongatus</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C130" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Phanerodon furcatus</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C131" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C132" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Glyptocephalus zachirus</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C133" t="n">
+        <v>177.827941</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Thaleichthys pacificus</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C134" t="n">
+        <v>177.827941</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Dendrobranchiata</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C135" t="n">
+        <v>173.780083</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Pandalus jordani</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C136" t="n">
+        <v>169.824365</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Marine groundfishes not identified</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C137" t="n">
+        <v>165.958691</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Microstomus pacificus</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C138" t="n">
+        <v>165.958691</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Atractoscion nobilis</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C139" t="n">
+        <v>162.18101</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sebastes jordani</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C140" t="n">
+        <v>158.489319</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Microstomus bathybius</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C141" t="n">
+        <v>158.489319</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Lepidopsetta bilineata</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C142" t="n">
+        <v>151.356125</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Clupea pallasii</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>144.543977</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Mallotus villosus</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C144" t="n">
+        <v>141.253754</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Ammodytidae</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="C145" t="n">
+        <v>128.824955</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Chionoecetes bairdi</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C146" t="n">
+        <v>120.226443</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C147" t="n">
+        <v>114.815362</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Engraulis mordax</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C148" t="n">
+        <v>93.32543</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sardinops sagax</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C149" t="n">
+        <v>69.183097</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Paralithodes</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C150" t="n">
+        <v>66.069345</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Lithodidae</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C151" t="n">
+        <v>66.069345</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Miscellaneous marine crustaceans</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C152" t="n">
+        <v>50.118723</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Pandalidae</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C153" t="n">
+        <v>50.118723</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Pandalus</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C154" t="n">
+        <v>39.810717</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Erimacrus isenbeckii</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C155" t="n">
+        <v>39.810717</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Brachyura</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C156" t="n">
+        <v>39.810717</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Miscellaneous aquatic invertebrates</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="C157" t="n">
+        <v>26.915348</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Mesocentrotus franciscanus</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C158" t="n">
+        <v>25.118864</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mya arenaria</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="C159" t="n">
+        <v>20.417379</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Strongylocentrotus droebachiensis</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C160" t="n">
+        <v>19.952623</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Chionoecetes</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C161" t="n">
+        <v>19.952623</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C162" t="n">
+        <v>16.982437</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Strongylocentrotus</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C163" t="n">
+        <v>12.589254</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Leukoma staminea</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>12.589254</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Clinocardium nuttallii</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C165" t="n">
+        <v>11.220185</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Tresus</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C166" t="n">
+        <v>10.715193</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Panopea generosa</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2</v>
+      </c>
+      <c r="C167" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Siliqua patula</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>2</v>
+      </c>
+      <c r="C168" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Veneridae</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>2</v>
+      </c>
+      <c r="C169" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Saxidomus gigantea</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>2</v>
+      </c>
+      <c r="C170" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Cardiidae</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2</v>
+      </c>
+      <c r="C171" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Magallana gigas</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Crassostrea</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Haliotis</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>2</v>
+      </c>
+      <c r="C174" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -53448,14 +55551,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -53499,14 +55602,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -53535,6 +55638,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53620,7 +55774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -91413,132 +93567,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Net primary production, 2019, tonnes carbon per year</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>satellite_model</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>npp_tC_yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Antoine-Morel</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>219993119.700814</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VGPM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>331249787.4592262</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Eppley</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>218207774.2933292</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CbPM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>310307011.5251073</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAFE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>211747433.3103423</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ensemble median</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>219993119.700814</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ensemble min</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>211747433.3103423</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ensemble max</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>331249787.4592262</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>water area (km2)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1443915.479997059</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>